--- a/output/pdf_financials_xlsx/ADK.xlsx
+++ b/output/pdf_financials_xlsx/ADK.xlsx
@@ -4518,28 +4518,28 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>0</v>
+        <v>-0.137667</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>-0.061583</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>-0.006</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>-0.024573</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>-0.053532</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>-0.053082</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>-0.053082</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>-0.053082</v>
       </c>
       <c r="J91" s="3" t="n">
         <v>0</v>
@@ -4563,37 +4563,37 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>5.843011</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>6.566927</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>6.865731</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>7.532632</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>8.169228</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>8.468301</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>8.737349999999999</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>9.175573999999999</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>9.588048000000001</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>9.822278000000001</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>10.129647</v>
       </c>
       <c r="M92" s="1" t="inlineStr">
         <is>
@@ -7888,7 +7888,11 @@
           <t>Reserve 13</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -9090,7 +9094,11 @@
           <t>Reserve 12</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -10080,7 +10088,11 @@
           <t>Reserve 14</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -10154,7 +10166,11 @@
           <t>Investments revaluation reserve</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E52" s="5" t="n">
         <v>-0.137667</v>
       </c>
@@ -10584,7 +10600,11 @@
           <t>Reserve 15</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -10736,7 +10756,11 @@
           <t>Investments revaluation reserve</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -11264,7 +11288,11 @@
           <t>Reserve 15</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -11416,7 +11444,11 @@
           <t>Investments revaluation reserve</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -12018,7 +12050,11 @@
           <t>Reserve 15</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -12092,7 +12128,11 @@
           <t>Investments revaluation reserve</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -12542,7 +12582,11 @@
           <t>Reserve 15</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -14268,7 +14312,11 @@
           <t>Reserve 16 7,532,632</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -15338,7 +15386,11 @@
           <t>Reserve 16, 26</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -18226,7 +18278,11 @@
           <t>Reserve 16</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E158" s="5" t="n">
         <v>5.843011</v>
       </c>

--- a/output/pdf_financials_xlsx/ADK.xlsx
+++ b/output/pdf_financials_xlsx/ADK.xlsx
@@ -1909,37 +1909,37 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.352105</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.477015</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.189861</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.150291</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.138242</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.570442</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.35939</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.420914</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.296639</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.219015</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.088722</v>
       </c>
       <c r="M34" s="1" t="inlineStr">
         <is>
@@ -1999,37 +1999,37 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.157263</v>
+        <v>0.509368</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.103686</v>
+        <v>0.580701</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.084827</v>
+        <v>0.274688</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.085984</v>
+        <v>0.236275</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.555712</v>
+        <v>0.693954</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1.301665</v>
+        <v>1.872107</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>1.001467</v>
+        <v>1.360857</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.5</v>
+        <v>0.920914</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.296639</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.219015</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>3.146656</v>
+        <v>3.235378</v>
       </c>
       <c r="M36" s="1" t="inlineStr">
         <is>
@@ -2539,37 +2539,37 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.401995</v>
+        <v>0.04989</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.52455</v>
+        <v>0.047535</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.221409</v>
+        <v>0.031548</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.172835</v>
+        <v>0.022544</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.146673</v>
+        <v>0.008430999999999999</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.692727</v>
+        <v>0.122285</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.385505</v>
+        <v>0.026115</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.442573</v>
+        <v>0.021659</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.311531</v>
+        <v>0.014892</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.2403</v>
+        <v>0.021285</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.148814</v>
+        <v>0.060092</v>
       </c>
       <c r="M48" s="1" t="inlineStr">
         <is>
@@ -5921,34 +5921,34 @@
         <v>0</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.003514</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.020625</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.028926</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.057151</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.096831</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.105828</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.086918</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.122364</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.13479</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.142561</v>
       </c>
     </row>
     <row r="125">
@@ -5964,34 +5964,34 @@
         <v>0</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.003514</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.020625</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.028926</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.057151</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.096831</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.105828</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.086918</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.122364</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.13479</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.142561</v>
       </c>
     </row>
     <row r="126">
@@ -6650,7 +6650,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -12734,7 +12734,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -19662,7 +19662,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -20970,7 +20974,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -23158,7 +23166,11 @@
           <t>Lease payments 11</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -24228,7 +24240,11 @@
           <t>Lease payments 13</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
@@ -25274,7 +25290,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -29622,7 +29642,11 @@
           <t>Lease payments 14</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -34058,7 +34082,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -34208,7 +34232,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -34840,7 +34864,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -35200,7 +35224,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -35648,7 +35672,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -36322,7 +36346,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E403" s="5" t="n">

--- a/output/pdf_financials_xlsx/ADK.xlsx
+++ b/output/pdf_financials_xlsx/ADK.xlsx
@@ -4883,19 +4883,19 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.017789</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.01883</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.025703</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.008544</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.000759</v>
       </c>
       <c r="G100" s="3" t="n">
         <v>0</v>
@@ -25750,7 +25750,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -27250,7 +27250,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -29198,7 +29198,11 @@
           <t>Additions to intangible assets 9</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E307" t="inlineStr">
         <is>
           <t>-</t>
@@ -32132,7 +32136,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E346" s="5" t="n">
@@ -32964,7 +32968,11 @@
           <t>Additions to intangible assets 10</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E357" s="5" t="n">
         <v>-0.014931</v>
       </c>
